--- a/Kenya.xlsx
+++ b/Kenya.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\harik\OneDrive\Desktop\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1495AC8C-E5EC-4A6C-A3D9-4559D13FDA57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E717547-8D5F-41F2-A29B-B9FCDEAA2C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Accommodation Cost (Adults)" sheetId="3" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="98">
   <si>
     <t>Location</t>
   </si>
@@ -64,19 +64,7 @@
     <t>Adult</t>
   </si>
   <si>
-    <t>Child (Age: 9-17 years)</t>
-  </si>
-  <si>
-    <t>Child (Age: 0-8 years)</t>
-  </si>
-  <si>
     <t>Lake Nakuru</t>
-  </si>
-  <si>
-    <t>Child (Age: 5-17 years)</t>
-  </si>
-  <si>
-    <t>Child (Age: 0-4 years)</t>
   </si>
   <si>
     <t>Travellers  Category</t>
@@ -345,6 +333,15 @@
   </si>
   <si>
     <t>Form Factor</t>
+  </si>
+  <si>
+    <t>Age from</t>
+  </si>
+  <si>
+    <t>Age to</t>
+  </si>
+  <si>
+    <t>Child</t>
   </si>
 </sst>
 </file>
@@ -807,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="G1" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
@@ -836,7 +833,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C2" s="10">
         <v>46097</v>
@@ -845,10 +842,10 @@
         <v>46188</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G2" s="9">
         <v>229</v>
@@ -865,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C3" s="10">
         <v>46097</v>
@@ -874,10 +871,10 @@
         <v>46188</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G3" s="9">
         <v>286</v>
@@ -894,7 +891,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C4" s="10">
         <v>46311</v>
@@ -903,10 +900,10 @@
         <v>46376</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G4" s="9">
         <v>229</v>
@@ -923,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C5" s="10">
         <v>46311</v>
@@ -932,10 +929,10 @@
         <v>46376</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G5" s="9">
         <v>286</v>
@@ -952,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" s="10">
         <v>46025</v>
@@ -961,10 +958,10 @@
         <v>46096</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G6" s="9">
         <v>260</v>
@@ -981,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C7" s="10">
         <v>46025</v>
@@ -990,10 +987,10 @@
         <v>46096</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G7" s="9">
         <v>328</v>
@@ -1010,7 +1007,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C8" s="10">
         <v>46189</v>
@@ -1019,10 +1016,10 @@
         <v>46203</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G8" s="9">
         <v>260</v>
@@ -1039,7 +1036,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C9" s="10">
         <v>46189</v>
@@ -1048,10 +1045,10 @@
         <v>46203</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G9" s="9">
         <v>328</v>
@@ -1068,7 +1065,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C10" s="10">
         <v>46296</v>
@@ -1077,10 +1074,10 @@
         <v>46310</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G10" s="9">
         <v>260</v>
@@ -1097,7 +1094,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C11" s="10">
         <v>46296</v>
@@ -1106,10 +1103,10 @@
         <v>46310</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G11" s="9">
         <v>328</v>
@@ -1126,7 +1123,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C12" s="10">
         <v>46204</v>
@@ -1135,10 +1132,10 @@
         <v>46295</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G12" s="9">
         <v>416</v>
@@ -1155,7 +1152,7 @@
         <v>4</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C13" s="10">
         <v>46204</v>
@@ -1164,10 +1161,10 @@
         <v>46295</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G13" s="9">
         <v>520</v>
@@ -1184,7 +1181,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C14" s="10">
         <v>46377</v>
@@ -1193,10 +1190,10 @@
         <v>46390</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G14" s="9">
         <v>416</v>
@@ -1213,7 +1210,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C15" s="10">
         <v>46377</v>
@@ -1222,10 +1219,10 @@
         <v>46390</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G15" s="9">
         <v>520</v>
@@ -1239,10 +1236,10 @@
     </row>
     <row r="16" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C16" s="13">
         <v>46007</v>
@@ -1251,10 +1248,10 @@
         <v>46112</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G16" s="12">
         <v>234</v>
@@ -1268,10 +1265,10 @@
     </row>
     <row r="17" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C17" s="13">
         <v>46113</v>
@@ -1280,10 +1277,10 @@
         <v>46203</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G17" s="12">
         <v>124</v>
@@ -1297,10 +1294,10 @@
     </row>
     <row r="18" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C18" s="13">
         <v>46204</v>
@@ -1309,10 +1306,10 @@
         <v>46265</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G18" s="12">
         <v>245</v>
@@ -1326,10 +1323,10 @@
     </row>
     <row r="19" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C19" s="13">
         <v>46266</v>
@@ -1338,10 +1335,10 @@
         <v>46371</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G19" s="12">
         <v>234</v>
@@ -1355,10 +1352,10 @@
     </row>
     <row r="20" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C20" s="13">
         <v>46007</v>
@@ -1367,10 +1364,10 @@
         <v>46112</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G20" s="12"/>
       <c r="H20" s="12">
@@ -1380,10 +1377,10 @@
     </row>
     <row r="21" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C21" s="13">
         <v>46113</v>
@@ -1392,10 +1389,10 @@
         <v>46203</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G21" s="12"/>
       <c r="H21" s="12">
@@ -1405,10 +1402,10 @@
     </row>
     <row r="22" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C22" s="13">
         <v>46204</v>
@@ -1417,10 +1414,10 @@
         <v>46265</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G22" s="12"/>
       <c r="H22" s="12">
@@ -1430,10 +1427,10 @@
     </row>
     <row r="23" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C23" s="13">
         <v>46266</v>
@@ -1442,10 +1439,10 @@
         <v>46371</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G23" s="12"/>
       <c r="H23" s="12">
@@ -1455,10 +1452,10 @@
     </row>
     <row r="24" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C24" s="13">
         <v>46007</v>
@@ -1467,10 +1464,10 @@
         <v>46112</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G24" s="12"/>
       <c r="H24" s="15">
@@ -1480,10 +1477,10 @@
     </row>
     <row r="25" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C25" s="13">
         <v>46113</v>
@@ -1492,10 +1489,10 @@
         <v>46203</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G25" s="12"/>
       <c r="H25" s="15">
@@ -1505,10 +1502,10 @@
     </row>
     <row r="26" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C26" s="13">
         <v>46204</v>
@@ -1517,10 +1514,10 @@
         <v>46265</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G26" s="12"/>
       <c r="H26" s="15">
@@ -1530,10 +1527,10 @@
     </row>
     <row r="27" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C27" s="13">
         <v>46266</v>
@@ -1542,10 +1539,10 @@
         <v>46371</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G27" s="12"/>
       <c r="H27" s="15">
@@ -1555,10 +1552,10 @@
     </row>
     <row r="28" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C28" s="10">
         <v>46007</v>
@@ -1567,10 +1564,10 @@
         <v>46112</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G28" s="9">
         <v>201</v>
@@ -1584,10 +1581,10 @@
     </row>
     <row r="29" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C29" s="10">
         <v>46113</v>
@@ -1596,10 +1593,10 @@
         <v>46203</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G29" s="9">
         <v>124</v>
@@ -1613,10 +1610,10 @@
     </row>
     <row r="30" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C30" s="10">
         <v>46204</v>
@@ -1625,10 +1622,10 @@
         <v>46265</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G30" s="9">
         <v>212</v>
@@ -1642,10 +1639,10 @@
     </row>
     <row r="31" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C31" s="10">
         <v>46266</v>
@@ -1654,10 +1651,10 @@
         <v>46371</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G31" s="9">
         <v>201</v>
@@ -1674,7 +1671,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C32" s="13">
         <v>46025</v>
@@ -1683,10 +1680,10 @@
         <v>46112</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G32" s="12">
         <v>130</v>
@@ -1703,7 +1700,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C33" s="13">
         <v>46113</v>
@@ -1712,10 +1709,10 @@
         <v>46187</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G33" s="12">
         <v>110</v>
@@ -1732,7 +1729,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C34" s="13">
         <v>46188</v>
@@ -1741,10 +1738,10 @@
         <v>46326</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G34" s="12">
         <v>160</v>
@@ -1761,7 +1758,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C35" s="13">
         <v>46327</v>
@@ -1770,10 +1767,10 @@
         <v>46377</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G35" s="12">
         <v>120</v>
@@ -1790,7 +1787,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C36" s="13">
         <v>46378</v>
@@ -1799,10 +1796,10 @@
         <v>46389</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G36" s="12">
         <v>160</v>
@@ -1819,7 +1816,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C37" s="10">
         <v>46025</v>
@@ -1828,10 +1825,10 @@
         <v>46173</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G37" s="9">
         <v>190</v>
@@ -1848,7 +1845,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C38" s="10">
         <v>46025</v>
@@ -1857,10 +1854,10 @@
         <v>46173</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G38" s="9">
         <v>190</v>
@@ -1877,7 +1874,7 @@
         <v>4</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C39" s="10">
         <v>46025</v>
@@ -1886,10 +1883,10 @@
         <v>46173</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G39" s="9">
         <v>120</v>
@@ -1904,7 +1901,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C40" s="10">
         <v>46174</v>
@@ -1913,10 +1910,10 @@
         <v>46295</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G40" s="9">
         <v>410</v>
@@ -1933,7 +1930,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C41" s="10">
         <v>46174</v>
@@ -1942,10 +1939,10 @@
         <v>46295</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G41" s="9">
         <v>390</v>
@@ -1962,7 +1959,7 @@
         <v>4</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C42" s="10">
         <v>46174</v>
@@ -1971,10 +1968,10 @@
         <v>46295</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G42" s="9">
         <v>190</v>
@@ -1989,7 +1986,7 @@
         <v>4</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C43" s="10">
         <v>46296</v>
@@ -1998,10 +1995,10 @@
         <v>46378</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G43" s="9">
         <v>190</v>
@@ -2018,7 +2015,7 @@
         <v>4</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C44" s="10">
         <v>46296</v>
@@ -2027,10 +2024,10 @@
         <v>46378</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G44" s="9">
         <v>190</v>
@@ -2047,7 +2044,7 @@
         <v>4</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C45" s="10">
         <v>46296</v>
@@ -2056,10 +2053,10 @@
         <v>46378</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G45" s="9">
         <v>120</v>
@@ -2074,7 +2071,7 @@
         <v>4</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C46" s="10">
         <v>46379</v>
@@ -2083,10 +2080,10 @@
         <v>46389</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G46" s="9">
         <v>410</v>
@@ -2103,7 +2100,7 @@
         <v>4</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C47" s="10">
         <v>46379</v>
@@ -2112,10 +2109,10 @@
         <v>46389</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G47" s="9">
         <v>490</v>
@@ -2132,7 +2129,7 @@
         <v>4</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C48" s="10">
         <v>46379</v>
@@ -2141,10 +2138,10 @@
         <v>46389</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G48" s="9">
         <v>250</v>
@@ -2159,7 +2156,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C49" s="13">
         <v>46025</v>
@@ -2168,10 +2165,10 @@
         <v>46081</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G49" s="12">
         <v>190</v>
@@ -2186,7 +2183,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C50" s="13">
         <v>46082</v>
@@ -2195,10 +2192,10 @@
         <v>46173</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G50" s="12">
         <v>145</v>
@@ -2213,7 +2210,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C51" s="13">
         <v>46174</v>
@@ -2222,10 +2219,10 @@
         <v>46203</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G51" s="12">
         <v>190</v>
@@ -2240,7 +2237,7 @@
         <v>4</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C52" s="13">
         <v>46204</v>
@@ -2249,10 +2246,10 @@
         <v>46295</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G52" s="12">
         <v>365</v>
@@ -2267,7 +2264,7 @@
         <v>4</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C53" s="13">
         <v>46296</v>
@@ -2276,10 +2273,10 @@
         <v>46326</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G53" s="12">
         <v>190</v>
@@ -2294,7 +2291,7 @@
         <v>4</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C54" s="13">
         <v>46327</v>
@@ -2303,10 +2300,10 @@
         <v>46356</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G54" s="12">
         <v>145</v>
@@ -2321,7 +2318,7 @@
         <v>4</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C55" s="13">
         <v>46357</v>
@@ -2330,10 +2327,10 @@
         <v>46375</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G55" s="12">
         <v>190</v>
@@ -2348,7 +2345,7 @@
         <v>4</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C56" s="13">
         <v>46376</v>
@@ -2357,10 +2354,10 @@
         <v>46389</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G56" s="12">
         <v>365</v>
@@ -2375,7 +2372,7 @@
         <v>4</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C57" s="13">
         <v>46025</v>
@@ -2384,10 +2381,10 @@
         <v>46081</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G57" s="12">
         <v>190</v>
@@ -2402,7 +2399,7 @@
         <v>4</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C58" s="13">
         <v>46082</v>
@@ -2411,10 +2408,10 @@
         <v>46173</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G58" s="12">
         <v>145</v>
@@ -2429,7 +2426,7 @@
         <v>4</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C59" s="13">
         <v>46174</v>
@@ -2438,10 +2435,10 @@
         <v>46203</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G59" s="12">
         <v>190</v>
@@ -2456,7 +2453,7 @@
         <v>4</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C60" s="13">
         <v>46204</v>
@@ -2465,10 +2462,10 @@
         <v>46295</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G60" s="12">
         <v>365</v>
@@ -2483,7 +2480,7 @@
         <v>4</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C61" s="13">
         <v>46296</v>
@@ -2492,10 +2489,10 @@
         <v>46326</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G61" s="12">
         <v>190</v>
@@ -2510,7 +2507,7 @@
         <v>4</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C62" s="13">
         <v>46327</v>
@@ -2519,10 +2516,10 @@
         <v>46356</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G62" s="12">
         <v>145</v>
@@ -2537,7 +2534,7 @@
         <v>4</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C63" s="13">
         <v>46357</v>
@@ -2546,10 +2543,10 @@
         <v>46375</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G63" s="12">
         <v>190</v>
@@ -2564,7 +2561,7 @@
         <v>4</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C64" s="13">
         <v>46376</v>
@@ -2573,10 +2570,10 @@
         <v>46389</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G64" s="12">
         <v>365</v>
@@ -2591,7 +2588,7 @@
         <v>4</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C65" s="13">
         <v>46025</v>
@@ -2600,10 +2597,10 @@
         <v>46081</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G65" s="12">
         <v>190</v>
@@ -2618,7 +2615,7 @@
         <v>4</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C66" s="13">
         <v>46082</v>
@@ -2627,10 +2624,10 @@
         <v>46173</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G66" s="12">
         <v>145</v>
@@ -2645,7 +2642,7 @@
         <v>4</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C67" s="13">
         <v>46174</v>
@@ -2654,10 +2651,10 @@
         <v>46203</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G67" s="12">
         <v>190</v>
@@ -2672,7 +2669,7 @@
         <v>4</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C68" s="13">
         <v>46204</v>
@@ -2681,10 +2678,10 @@
         <v>46295</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G68" s="12">
         <v>365</v>
@@ -2699,7 +2696,7 @@
         <v>4</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C69" s="13">
         <v>46296</v>
@@ -2708,10 +2705,10 @@
         <v>46326</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G69" s="12">
         <v>190</v>
@@ -2726,7 +2723,7 @@
         <v>4</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C70" s="13">
         <v>46327</v>
@@ -2735,10 +2732,10 @@
         <v>46356</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G70" s="12">
         <v>145</v>
@@ -2753,7 +2750,7 @@
         <v>4</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C71" s="13">
         <v>46357</v>
@@ -2762,10 +2759,10 @@
         <v>46375</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G71" s="12">
         <v>190</v>
@@ -2780,7 +2777,7 @@
         <v>4</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C72" s="13">
         <v>46376</v>
@@ -2789,10 +2786,10 @@
         <v>46389</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G72" s="12">
         <v>365</v>
@@ -2807,7 +2804,7 @@
         <v>4</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C73" s="28">
         <v>46025</v>
@@ -2816,10 +2813,10 @@
         <v>46081</v>
       </c>
       <c r="E73" s="27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F73" s="27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G73" s="27">
         <v>160</v>
@@ -2834,7 +2831,7 @@
         <v>4</v>
       </c>
       <c r="B74" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C74" s="28">
         <v>46082</v>
@@ -2843,10 +2840,10 @@
         <v>46112</v>
       </c>
       <c r="E74" s="27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F74" s="27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G74" s="27">
         <v>120</v>
@@ -2861,7 +2858,7 @@
         <v>4</v>
       </c>
       <c r="B75" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C75" s="28">
         <v>46174</v>
@@ -2870,10 +2867,10 @@
         <v>46203</v>
       </c>
       <c r="E75" s="27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F75" s="27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G75" s="27">
         <v>160</v>
@@ -2888,7 +2885,7 @@
         <v>4</v>
       </c>
       <c r="B76" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C76" s="28">
         <v>46204</v>
@@ -2897,10 +2894,10 @@
         <v>46295</v>
       </c>
       <c r="E76" s="27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F76" s="27" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G76" s="27">
         <v>260</v>
@@ -2915,7 +2912,7 @@
         <v>4</v>
       </c>
       <c r="B77" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C77" s="28">
         <v>46296</v>
@@ -2924,10 +2921,10 @@
         <v>46326</v>
       </c>
       <c r="E77" s="27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F77" s="27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G77" s="27">
         <v>160</v>
@@ -2942,7 +2939,7 @@
         <v>4</v>
       </c>
       <c r="B78" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C78" s="28">
         <v>46357</v>
@@ -2951,10 +2948,10 @@
         <v>46375</v>
       </c>
       <c r="E78" s="27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F78" s="27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G78" s="27">
         <v>160</v>
@@ -2969,7 +2966,7 @@
         <v>4</v>
       </c>
       <c r="B79" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C79" s="28">
         <v>46376</v>
@@ -2978,10 +2975,10 @@
         <v>46389</v>
       </c>
       <c r="E79" s="27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F79" s="27" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G79" s="27">
         <v>260</v>
@@ -2996,7 +2993,7 @@
         <v>4</v>
       </c>
       <c r="B80" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C80" s="28">
         <v>46025</v>
@@ -3005,10 +3002,10 @@
         <v>46081</v>
       </c>
       <c r="E80" s="27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F80" s="27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G80" s="27">
         <v>160</v>
@@ -3023,7 +3020,7 @@
         <v>4</v>
       </c>
       <c r="B81" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C81" s="28">
         <v>46082</v>
@@ -3032,10 +3029,10 @@
         <v>46112</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F81" s="27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G81" s="27">
         <v>120</v>
@@ -3050,7 +3047,7 @@
         <v>4</v>
       </c>
       <c r="B82" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C82" s="28">
         <v>46174</v>
@@ -3059,10 +3056,10 @@
         <v>46203</v>
       </c>
       <c r="E82" s="27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F82" s="27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G82" s="27">
         <v>160</v>
@@ -3077,7 +3074,7 @@
         <v>4</v>
       </c>
       <c r="B83" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C83" s="28">
         <v>46204</v>
@@ -3086,10 +3083,10 @@
         <v>46295</v>
       </c>
       <c r="E83" s="27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F83" s="27" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G83" s="27">
         <v>260</v>
@@ -3104,7 +3101,7 @@
         <v>4</v>
       </c>
       <c r="B84" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C84" s="28">
         <v>46296</v>
@@ -3113,10 +3110,10 @@
         <v>46326</v>
       </c>
       <c r="E84" s="27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F84" s="27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G84" s="27">
         <v>160</v>
@@ -3131,7 +3128,7 @@
         <v>4</v>
       </c>
       <c r="B85" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C85" s="28">
         <v>46357</v>
@@ -3140,10 +3137,10 @@
         <v>46375</v>
       </c>
       <c r="E85" s="27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F85" s="27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G85" s="27">
         <v>160</v>
@@ -3158,7 +3155,7 @@
         <v>4</v>
       </c>
       <c r="B86" s="27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C86" s="28">
         <v>46376</v>
@@ -3167,10 +3164,10 @@
         <v>46389</v>
       </c>
       <c r="E86" s="27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F86" s="27" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G86" s="27">
         <v>260</v>
@@ -9294,7 +9291,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE3F4C7-1820-4B0C-9457-C8F06B693E11}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
@@ -9310,19 +9307,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -9330,7 +9327,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C2" s="6">
         <v>0</v>
@@ -9339,7 +9336,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F2" s="7">
         <v>0</v>
@@ -9350,7 +9347,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C3" s="6">
         <v>4</v>
@@ -9359,7 +9356,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F3" s="7">
         <v>0.5</v>
@@ -9370,16 +9367,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C4" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D4" s="6">
         <v>17</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F4" s="7">
         <v>0.75</v>
@@ -9387,10 +9384,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4">
         <v>0</v>
@@ -9399,7 +9396,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F5" s="7">
         <v>0</v>
@@ -9407,10 +9404,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4">
         <v>3</v>
@@ -9419,7 +9416,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F6" s="7">
         <v>0.5</v>
@@ -9427,62 +9424,62 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
-        <v>2</v>
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4">
+        <v>12</v>
+      </c>
+      <c r="D7" s="4">
+        <v>17</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="7">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C8" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D8" s="6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F8" s="7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C9" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F9" s="7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -9490,19 +9487,19 @@
         <v>4</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C10" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="6">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F10" s="7">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -9510,19 +9507,19 @@
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C11" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" s="6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" s="7">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -9530,39 +9527,39 @@
         <v>4</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C12" s="6">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6">
         <v>4</v>
       </c>
-      <c r="D12" s="6">
+      <c r="E12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="6">
+        <v>4</v>
+      </c>
+      <c r="D13" s="6">
         <v>12</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="E13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="7">
         <v>0.75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="4">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4">
-        <v>4</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13" s="7">
-        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -9570,19 +9567,19 @@
         <v>4</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C14" s="4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F14" s="7">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -9590,19 +9587,19 @@
         <v>4</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C15" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D15" s="4">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F15" s="7">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -9610,18 +9607,38 @@
         <v>4</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C16" s="4">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>4</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="4">
         <v>5</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D17" s="4">
         <v>16</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="7">
+      <c r="E17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="7">
         <v>0.75</v>
       </c>
     </row>
@@ -9632,7 +9649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -9640,15 +9657,15 @@
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.109375" customWidth="1"/>
     <col min="5" max="5" width="43.44140625" customWidth="1"/>
-    <col min="6" max="6" width="31.6640625" customWidth="1"/>
+    <col min="6" max="6" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -9660,15 +9677,21 @@
         <v>3</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5">
         <v>46023</v>
@@ -9682,13 +9705,19 @@
       <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="4">
+        <v>18</v>
+      </c>
+      <c r="H2" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5">
         <v>46204</v>
@@ -9702,13 +9731,19 @@
       <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="4">
+        <v>18</v>
+      </c>
+      <c r="H3" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5">
         <v>46023</v>
@@ -9720,15 +9755,21 @@
         <v>50</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="G4" s="4">
+        <v>9</v>
+      </c>
+      <c r="H4" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C5" s="5">
         <v>46023</v>
@@ -9740,15 +9781,21 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C6" s="5">
         <v>46023</v>
@@ -9762,13 +9809,19 @@
       <c r="F6" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6" s="4">
+        <v>18</v>
+      </c>
+      <c r="H6" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C7" s="5">
         <v>46023</v>
@@ -9780,15 +9833,21 @@
         <v>90</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" s="4">
+        <v>5</v>
+      </c>
+      <c r="H7" s="4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>13</v>
       </c>
       <c r="C8" s="5">
         <v>46023</v>
@@ -9800,7 +9859,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>10</v>
+        <v>97</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9820,10 +9885,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -9831,13 +9896,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6">
         <v>230</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -9856,15 +9921,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B2" s="6">
         <v>200</v>
@@ -9890,22 +9955,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>0</v>
@@ -9913,22 +9978,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B2" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>4</v>
@@ -9936,68 +10001,68 @@
     </row>
     <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>4</v>
@@ -10005,22 +10070,22 @@
     </row>
     <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G6" s="23" t="s">
         <v>4</v>
@@ -10028,25 +10093,25 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="D7" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>93</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
